--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_ADJR2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\SEC\ratio.alpha.beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -227,7 +227,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -235,31 +235,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -632,49 +616,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C2">
-        <v>-3.4797002392697153E-2</v>
+        <v>-3.4796998232330907E-2</v>
       </c>
       <c r="D2">
-        <v>-5.3852362548961433E-2</v>
+        <v>-5.3852390280210362E-2</v>
       </c>
       <c r="E2">
-        <v>-5.9897405745343912E-2</v>
+        <v>-5.9897411669500307E-2</v>
       </c>
       <c r="F2">
-        <v>-6.1285748729154002E-2</v>
+        <v>-6.1285739897219922E-2</v>
       </c>
       <c r="G2">
-        <v>-6.0727227790227677E-2</v>
+        <v>-6.072721653017786E-2</v>
       </c>
       <c r="H2">
-        <v>-6.2178301385081472E-2</v>
+        <v>-6.2178292070992729E-2</v>
       </c>
       <c r="I2">
-        <v>3.2733503322159231E-3</v>
+        <v>3.2733596639955599E-3</v>
       </c>
       <c r="J2">
-        <v>9.2123928561410856E-2</v>
+        <v>9.2123937817835899E-2</v>
       </c>
       <c r="K2">
-        <v>4.8668925423998109E-2</v>
+        <v>4.8668938706028141E-2</v>
       </c>
       <c r="L2">
-        <v>9.7722210924029565E-2</v>
+        <v>9.7722219312003089E-2</v>
       </c>
       <c r="M2">
-        <v>0.1849994568601051</v>
+        <v>0.18499945935423451</v>
       </c>
       <c r="N2">
-        <v>0.2213144588893225</v>
+        <v>0.2213144735208008</v>
       </c>
       <c r="O2">
-        <v>0.3042350444268288</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0.38351382896663039</v>
+        <v>0.30423506605844658</v>
+      </c>
+      <c r="P2">
+        <v>0.38351386044565072</v>
       </c>
       <c r="Q2">
-        <v>0.42237281923662878</v>
+        <v>0.42237285900884552</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -685,49 +669,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C3">
-        <v>-2.297019530262016E-2</v>
+        <v>-2.2970195240494741E-2</v>
       </c>
       <c r="D3">
-        <v>-4.5968467411213298E-2</v>
+        <v>-4.5968462150039691E-2</v>
       </c>
       <c r="E3">
-        <v>-0.17678579464570121</v>
+        <v>-0.17678580847881059</v>
       </c>
       <c r="F3">
-        <v>1.327218200258222E-2</v>
+        <v>1.3272166458149741E-2</v>
       </c>
       <c r="G3">
-        <v>0.10109382899849589</v>
+        <v>0.10109382631293951</v>
       </c>
       <c r="H3">
-        <v>0.17035300497168901</v>
+        <v>0.17035300215570209</v>
       </c>
       <c r="I3">
-        <v>0.22259255523281901</v>
+        <v>0.22259249349513011</v>
       </c>
       <c r="J3">
-        <v>0.23866441819276701</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0.30015143523084759</v>
+        <v>0.23866439624510369</v>
+      </c>
+      <c r="K3">
+        <v>0.30015143233162561</v>
       </c>
       <c r="L3">
-        <v>0.34401284560681411</v>
+        <v>0.34401285799256842</v>
       </c>
       <c r="M3">
-        <v>0.34039027330502369</v>
+        <v>0.3403903072319221</v>
       </c>
       <c r="N3">
-        <v>0.34642699295282792</v>
+        <v>0.34642706827060799</v>
       </c>
       <c r="O3">
-        <v>0.31375452773715001</v>
+        <v>0.31375467362049608</v>
       </c>
       <c r="P3">
-        <v>0.30866869115975087</v>
+        <v>0.3086689304342054</v>
       </c>
       <c r="Q3">
-        <v>0.3385053742875852</v>
+        <v>0.33850568411028747</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -738,49 +722,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C4">
-        <v>-3.0529963701704431E-2</v>
+        <v>-3.052996094336425E-2</v>
       </c>
       <c r="D4">
-        <v>-4.633740859492419E-2</v>
+        <v>-4.6337332411850951E-2</v>
       </c>
       <c r="E4">
-        <v>-0.13210348132686009</v>
+        <v>-0.13210347531939279</v>
       </c>
       <c r="F4">
-        <v>-0.13446472951722441</v>
+        <v>-0.1344647094910989</v>
       </c>
       <c r="G4">
-        <v>-0.20493173416039301</v>
+        <v>-0.20493173740932669</v>
       </c>
       <c r="H4">
-        <v>-6.1143796807262507E-2</v>
+        <v>-6.114376160883616E-2</v>
       </c>
       <c r="I4">
-        <v>8.9102429296634783E-2</v>
+        <v>8.9102463486679315E-2</v>
       </c>
       <c r="J4">
-        <v>0.1124041020806935</v>
+        <v>0.1124041236715061</v>
       </c>
       <c r="K4">
-        <v>0.12817378062137019</v>
+        <v>0.12817380604206219</v>
       </c>
       <c r="L4">
-        <v>0.2045379271530105</v>
+        <v>0.20453795113973799</v>
       </c>
       <c r="M4">
-        <v>0.27391927099005747</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0.33352378803126748</v>
+        <v>0.27391929705233842</v>
+      </c>
+      <c r="N4">
+        <v>0.33352381496933159</v>
       </c>
       <c r="O4">
-        <v>0.37164408117120118</v>
+        <v>0.37164411166749378</v>
       </c>
       <c r="P4">
-        <v>0.38461116074320839</v>
+        <v>0.38461118598617289</v>
       </c>
       <c r="Q4">
-        <v>0.377970184491979</v>
+        <v>0.37797021075689691</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -791,49 +775,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C5">
-        <v>-2.5592421513200379E-2</v>
+        <v>-2.5592419824805309E-2</v>
       </c>
       <c r="D5">
-        <v>-7.5823678327988614E-2</v>
+        <v>-7.5823682898936595E-2</v>
       </c>
       <c r="E5">
-        <v>-8.6703235843808721E-2</v>
+        <v>-8.6703226827865701E-2</v>
       </c>
       <c r="F5">
-        <v>-0.13410967754853961</v>
+        <v>-0.13410967537868279</v>
       </c>
       <c r="G5">
-        <v>8.5679900056743544E-2</v>
+        <v>8.5679903246940151E-2</v>
       </c>
       <c r="H5">
-        <v>0.18077210974006719</v>
+        <v>0.180772120768982</v>
       </c>
       <c r="I5">
-        <v>0.2322684848636255</v>
+        <v>0.23226848936947039</v>
       </c>
       <c r="J5">
-        <v>0.29811458586599782</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.37031066127109269</v>
+        <v>0.29811460714867949</v>
+      </c>
+      <c r="K5">
+        <v>0.37031066740281537</v>
       </c>
       <c r="L5">
-        <v>0.40789063508637707</v>
+        <v>0.40789066577873467</v>
       </c>
       <c r="M5">
-        <v>0.44791958086994171</v>
+        <v>0.4479196277524099</v>
       </c>
       <c r="N5">
-        <v>0.44721981160569529</v>
+        <v>0.44721988156079001</v>
       </c>
       <c r="O5">
-        <v>0.42620211586171591</v>
+        <v>0.42620219446977098</v>
       </c>
       <c r="P5">
-        <v>0.40199667259052241</v>
+        <v>0.40199676727138489</v>
       </c>
       <c r="Q5">
-        <v>0.37961432208467799</v>
+        <v>0.37961445058011167</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -844,49 +828,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C6">
-        <v>-2.5850253404275259E-2</v>
+        <v>-2.5850251788448929E-2</v>
       </c>
       <c r="D6">
-        <v>-7.6382791013304432E-2</v>
+        <v>-7.6382801091711028E-2</v>
       </c>
       <c r="E6">
-        <v>-8.6185639666446878E-2</v>
+        <v>-8.6185633584171903E-2</v>
       </c>
       <c r="F6">
-        <v>-6.9191177121966416E-2</v>
+        <v>-6.9191192609653673E-2</v>
       </c>
       <c r="G6">
-        <v>0.16709037260646131</v>
+        <v>0.1670903719138398</v>
       </c>
       <c r="H6">
-        <v>0.28760506680778042</v>
+        <v>0.28760508498729409</v>
       </c>
       <c r="I6">
-        <v>0.33725096249828468</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.40921813673547358</v>
+        <v>0.33725096992266268</v>
+      </c>
+      <c r="J6">
+        <v>0.40921815317360138</v>
       </c>
       <c r="K6">
-        <v>0.45395614605220791</v>
+        <v>0.45395617413406192</v>
       </c>
       <c r="L6">
-        <v>0.47327413088068482</v>
+        <v>0.47327415502417092</v>
       </c>
       <c r="M6">
-        <v>0.49241507238240562</v>
+        <v>0.49241509913539139</v>
       </c>
       <c r="N6">
-        <v>0.49869984312262078</v>
+        <v>0.49869987534077997</v>
       </c>
       <c r="O6">
-        <v>0.49061169270194049</v>
+        <v>0.49061173467849079</v>
       </c>
       <c r="P6">
-        <v>0.49498387994264659</v>
+        <v>0.49498392957333398</v>
       </c>
       <c r="Q6">
-        <v>0.47808860452312268</v>
+        <v>0.47808865340179751</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -897,49 +881,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C7">
-        <v>-3.5313416952168407E-2</v>
+        <v>-3.5313414366568693E-2</v>
       </c>
       <c r="D7">
-        <v>-5.0760234490325358E-2</v>
+        <v>-5.0760232157602357E-2</v>
       </c>
       <c r="E7">
-        <v>-0.13980099710194779</v>
+        <v>-0.13980098496748319</v>
       </c>
       <c r="F7">
-        <v>-0.15229786172990081</v>
+        <v>-0.15229784225114509</v>
       </c>
       <c r="G7">
-        <v>-0.19872465324562799</v>
+        <v>-0.19872466140160239</v>
       </c>
       <c r="H7">
-        <v>-0.1975640377042476</v>
+        <v>-0.1975640448414322</v>
       </c>
       <c r="I7">
-        <v>-3.7333180360937239E-2</v>
+        <v>-3.7333235238839788E-2</v>
       </c>
       <c r="J7">
-        <v>8.5229553613779374E-2</v>
+        <v>8.5229558935943445E-2</v>
       </c>
       <c r="K7">
-        <v>8.4434355404679126E-2</v>
+        <v>8.4434385144323942E-2</v>
       </c>
       <c r="L7">
-        <v>0.1343547276286095</v>
+        <v>0.13435475013807019</v>
       </c>
       <c r="M7">
-        <v>0.2210376551103917</v>
+        <v>0.2210376889117156</v>
       </c>
       <c r="N7">
-        <v>0.29618177589191702</v>
+        <v>0.29618181451062708</v>
       </c>
       <c r="O7">
-        <v>0.35418515249969318</v>
+        <v>0.35418518661267839</v>
       </c>
       <c r="P7">
-        <v>0.38851983610111662</v>
+        <v>0.38851987361902851</v>
       </c>
       <c r="Q7">
-        <v>0.40344506769835708</v>
+        <v>0.40344510442477488</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -950,49 +934,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C8">
-        <v>-3.0673373728049659E-2</v>
+        <v>-3.0673371852327509E-2</v>
       </c>
       <c r="D8">
-        <v>-4.5154341286073638E-2</v>
+        <v>-4.5154341835079291E-2</v>
       </c>
       <c r="E8">
-        <v>-0.12013862621396559</v>
+        <v>-0.120138617643801</v>
       </c>
       <c r="F8">
-        <v>-0.14570452630148709</v>
+        <v>-0.14570452623236929</v>
       </c>
       <c r="G8">
-        <v>-8.8832582090157319E-2</v>
+        <v>-8.8832560209091554E-2</v>
       </c>
       <c r="H8">
-        <v>5.0141516426768758E-3</v>
+        <v>5.0141671957533778E-3</v>
       </c>
       <c r="I8">
-        <v>6.1920897621795049E-2</v>
+        <v>6.1920941818989987E-2</v>
       </c>
       <c r="J8">
-        <v>0.15520919564922339</v>
+        <v>0.15520921003464169</v>
       </c>
       <c r="K8">
-        <v>0.19761458331770529</v>
+        <v>0.19761459857275321</v>
       </c>
       <c r="L8">
-        <v>0.31732831697652147</v>
+        <v>0.31732834736179139</v>
       </c>
       <c r="M8">
-        <v>0.31967382676367501</v>
+        <v>0.31967385972626677</v>
       </c>
       <c r="N8">
-        <v>0.36861382987531249</v>
+        <v>0.36861386050693129</v>
       </c>
       <c r="O8">
-        <v>0.40761368752620752</v>
+        <v>0.40761371955380682</v>
       </c>
       <c r="P8">
-        <v>0.40652458139807202</v>
+        <v>0.40652461348776131</v>
       </c>
       <c r="Q8">
-        <v>0.40178598509664459</v>
+        <v>0.40178602906889899</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1003,49 +987,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C9">
-        <v>-2.8356694345300741E-2</v>
+        <v>-2.8356692576343011E-2</v>
       </c>
       <c r="D9">
-        <v>-4.4029789519784583E-2</v>
+        <v>-4.4029788327734617E-2</v>
       </c>
       <c r="E9">
-        <v>-0.1113572878225689</v>
+        <v>-0.11135727599585141</v>
       </c>
       <c r="F9">
-        <v>-0.1386696164190733</v>
+        <v>-0.13866961852662801</v>
       </c>
       <c r="G9">
-        <v>-8.0016407876304485E-2</v>
+        <v>-8.0016396036207305E-2</v>
       </c>
       <c r="H9">
-        <v>1.211071514087647E-2</v>
+        <v>1.211073035841421E-2</v>
       </c>
       <c r="I9">
-        <v>6.3673143171865773E-2</v>
+        <v>6.3673149616289254E-2</v>
       </c>
       <c r="J9">
-        <v>0.15571799775814199</v>
+        <v>0.15571801419742751</v>
       </c>
       <c r="K9">
-        <v>0.19852559876529699</v>
+        <v>0.19852562311392119</v>
       </c>
       <c r="L9">
-        <v>0.36400121847479838</v>
+        <v>0.36400123657163153</v>
       </c>
       <c r="M9">
-        <v>0.37195380508948789</v>
+        <v>0.37195381925432869</v>
       </c>
       <c r="N9">
-        <v>0.40838180321310169</v>
+        <v>0.40838182115562932</v>
       </c>
       <c r="O9">
-        <v>0.44323109846547692</v>
+        <v>0.44323111432192092</v>
       </c>
       <c r="P9">
-        <v>0.45380873073644901</v>
+        <v>0.4538087359861272</v>
       </c>
       <c r="Q9">
-        <v>0.45459008525786571</v>
+        <v>0.45459008946510499</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1056,49 +1040,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C10">
-        <v>-2.6691510416025459E-2</v>
+        <v>-2.669150881312134E-2</v>
       </c>
       <c r="D10">
-        <v>-4.1858118338935532E-2</v>
+        <v>-4.1858116068646027E-2</v>
       </c>
       <c r="E10">
-        <v>-0.1202150650534201</v>
+        <v>-0.1202150530129273</v>
       </c>
       <c r="F10">
-        <v>-0.14060563264021159</v>
+        <v>-0.1406056330616027</v>
       </c>
       <c r="G10">
-        <v>-8.8858877643691797E-2</v>
+        <v>-8.8858861901878181E-2</v>
       </c>
       <c r="H10">
-        <v>4.061695245481692E-3</v>
+        <v>4.0617129693045692E-3</v>
       </c>
       <c r="I10">
-        <v>6.2055296756127233E-2</v>
+        <v>6.2055308806162487E-2</v>
       </c>
       <c r="J10">
-        <v>0.153900068892805</v>
+        <v>0.1539000921113429</v>
       </c>
       <c r="K10">
-        <v>0.19003576239502121</v>
+        <v>0.1900357903851651</v>
       </c>
       <c r="L10">
-        <v>0.35082957137821158</v>
+        <v>0.3508295927443818</v>
       </c>
       <c r="M10">
-        <v>0.35496222479345929</v>
+        <v>0.3549622402925533</v>
       </c>
       <c r="N10">
-        <v>0.3917028893041955</v>
+        <v>0.39170290479115177</v>
       </c>
       <c r="O10">
-        <v>0.42227299535301099</v>
+        <v>0.42227301162565561</v>
       </c>
       <c r="P10">
-        <v>0.43369366094920292</v>
+        <v>0.43369366795419217</v>
       </c>
       <c r="Q10">
-        <v>0.43841669395064897</v>
+        <v>0.43841670732670751</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1109,49 +1093,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C11">
-        <v>-3.1722724002114053E-2</v>
+        <v>-3.172272263770673E-2</v>
       </c>
       <c r="D11">
-        <v>-4.8243464234574977E-2</v>
+        <v>-4.8243462879518591E-2</v>
       </c>
       <c r="E11">
-        <v>-0.11861049016000159</v>
+        <v>-0.1186104783500896</v>
       </c>
       <c r="F11">
-        <v>-0.14389686322462991</v>
+        <v>-0.1438968629004351</v>
       </c>
       <c r="G11">
-        <v>-8.6595925314043143E-2</v>
+        <v>-8.6595904549573666E-2</v>
       </c>
       <c r="H11">
-        <v>1.544607639932838E-3</v>
+        <v>1.5446148188886699E-3</v>
       </c>
       <c r="I11">
-        <v>5.2442021193440748E-2</v>
+        <v>5.244201850322143E-2</v>
       </c>
       <c r="J11">
-        <v>0.15932834764442569</v>
+        <v>0.15932837033714489</v>
       </c>
       <c r="K11">
-        <v>0.19951507232676691</v>
+        <v>0.19951510856332089</v>
       </c>
       <c r="L11">
-        <v>0.36551557385989808</v>
+        <v>0.36551557074073582</v>
       </c>
       <c r="M11">
-        <v>0.37553916005814209</v>
+        <v>0.3755391755607187</v>
       </c>
       <c r="N11">
-        <v>0.41103313543729492</v>
+        <v>0.41103316050170408</v>
       </c>
       <c r="O11">
-        <v>0.44224312108231528</v>
+        <v>0.44224314480998089</v>
       </c>
       <c r="P11">
-        <v>0.4454911941956563</v>
+        <v>0.44549121186234392</v>
       </c>
       <c r="Q11">
-        <v>0.44922050570578442</v>
+        <v>0.44922055903650748</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1162,49 +1146,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C12">
-        <v>-2.6756720230699811E-2</v>
+        <v>-2.6756718556157251E-2</v>
       </c>
       <c r="D12">
-        <v>-8.262445416798482E-2</v>
+        <v>-8.2624459624374452E-2</v>
       </c>
       <c r="E12">
-        <v>-6.0555781754641248E-2</v>
+        <v>-6.0555773195774543E-2</v>
       </c>
       <c r="F12">
-        <v>-0.1126078056758581</v>
+        <v>-0.11260780867528961</v>
       </c>
       <c r="G12">
-        <v>8.3038805885201808E-2</v>
+        <v>8.3038799662859597E-2</v>
       </c>
       <c r="H12">
-        <v>0.1619302490917523</v>
+        <v>0.16193026387025361</v>
       </c>
       <c r="I12">
-        <v>0.26282856067089871</v>
+        <v>0.26282857257014308</v>
       </c>
       <c r="J12">
-        <v>0.3562546814911533</v>
-      </c>
-      <c r="K12" s="2">
-        <v>0.4022152290171252</v>
+        <v>0.35625471360620498</v>
+      </c>
+      <c r="K12">
+        <v>0.40221526509828709</v>
       </c>
       <c r="L12">
-        <v>0.4291391883754393</v>
+        <v>0.42913922352796458</v>
       </c>
       <c r="M12">
-        <v>0.46742864352927838</v>
+        <v>0.46742870328468122</v>
       </c>
       <c r="N12">
-        <v>0.4703000350486054</v>
+        <v>0.47030010402694827</v>
       </c>
       <c r="O12">
-        <v>0.45601466572009841</v>
+        <v>0.45601475250631751</v>
       </c>
       <c r="P12">
-        <v>0.43238126119911929</v>
+        <v>0.43238136269328947</v>
       </c>
       <c r="Q12">
-        <v>0.39357848338742141</v>
+        <v>0.39357863096689072</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1215,49 +1199,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C13">
-        <v>-2.3893721743971318E-2</v>
+        <v>-2.3893720320706292E-2</v>
       </c>
       <c r="D13">
-        <v>-0.1201995310818109</v>
+        <v>-0.1201995368113233</v>
       </c>
       <c r="E13">
-        <v>-0.11278582961699091</v>
+        <v>-0.112785821703292</v>
       </c>
       <c r="F13">
-        <v>-0.1307710511099584</v>
+        <v>-0.13077106419370879</v>
       </c>
       <c r="G13">
-        <v>-0.16347516271622001</v>
+        <v>-0.16347519261660201</v>
       </c>
       <c r="H13">
-        <v>-2.0014291255418079E-2</v>
+        <v>-2.001430509131415E-2</v>
       </c>
       <c r="I13">
-        <v>4.5532055195594617E-3</v>
+        <v>4.5531931522426279E-3</v>
       </c>
       <c r="J13">
-        <v>6.9493762777614793E-2</v>
+        <v>6.9493752007350279E-2</v>
       </c>
       <c r="K13">
-        <v>0.1507475264948315</v>
+        <v>0.1507475533145434</v>
       </c>
       <c r="L13">
-        <v>0.2255624104650143</v>
+        <v>0.22556245919183521</v>
       </c>
       <c r="M13">
-        <v>0.2468114642571993</v>
+        <v>0.2468115233004245</v>
       </c>
       <c r="N13">
-        <v>0.27164830868655371</v>
+        <v>0.27164838970131661</v>
       </c>
       <c r="O13">
-        <v>0.27999002813846402</v>
+        <v>0.2799901323528427</v>
       </c>
       <c r="P13">
-        <v>0.29211798403815659</v>
+        <v>0.2921181368620811</v>
       </c>
       <c r="Q13">
-        <v>0.27158588194184802</v>
+        <v>0.27158607941221202</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1268,49 +1252,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C14">
-        <v>-3.2056823448559507E-2</v>
+        <v>-3.2056819736397242E-2</v>
       </c>
       <c r="D14">
-        <v>-4.9977206476293293E-2</v>
+        <v>-4.997720143126276E-2</v>
       </c>
       <c r="E14">
-        <v>-0.13529196978565361</v>
+        <v>-0.1352919604521276</v>
       </c>
       <c r="F14">
-        <v>-0.13787255983699709</v>
+        <v>-0.13787253981225989</v>
       </c>
       <c r="G14">
-        <v>-0.1823612950722413</v>
+        <v>-0.1823612911787198</v>
       </c>
       <c r="H14">
-        <v>-0.17215583078290531</v>
+        <v>-0.17215583325098949</v>
       </c>
       <c r="I14">
-        <v>-2.6109325064025461E-2</v>
+        <v>-2.610931046476932E-2</v>
       </c>
       <c r="J14">
-        <v>9.5030643239301923E-2</v>
+        <v>9.5030662563977117E-2</v>
       </c>
       <c r="K14">
-        <v>9.8049628573444791E-2</v>
+        <v>9.8049654806597789E-2</v>
       </c>
       <c r="L14">
-        <v>0.13550138432443859</v>
+        <v>0.13550141482556849</v>
       </c>
       <c r="M14">
-        <v>0.2422404537912515</v>
+        <v>0.24224049351180649</v>
       </c>
       <c r="N14">
-        <v>0.35216079953019808</v>
+        <v>0.35216082304149843</v>
       </c>
       <c r="O14">
-        <v>0.39231027238477828</v>
+        <v>0.39231029790193089</v>
       </c>
       <c r="P14">
-        <v>0.42180983474555628</v>
+        <v>0.4218098657650789</v>
       </c>
       <c r="Q14">
-        <v>0.43752674323861679</v>
+        <v>0.43752677194704193</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1321,49 +1305,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C15">
-        <v>-3.225698793633059E-2</v>
+        <v>-3.2256984753945277E-2</v>
       </c>
       <c r="D15">
-        <v>-4.6693587386558801E-2</v>
+        <v>-4.669358611612854E-2</v>
       </c>
       <c r="E15">
-        <v>-0.13015989213235801</v>
+        <v>-0.13015988110983831</v>
       </c>
       <c r="F15">
-        <v>-0.13403521419605441</v>
+        <v>-0.13403519593110211</v>
       </c>
       <c r="G15">
-        <v>-0.1732111876770267</v>
+        <v>-0.17321117876195019</v>
       </c>
       <c r="H15">
-        <v>-0.16227235910349719</v>
+        <v>-0.162272340220802</v>
       </c>
       <c r="I15">
-        <v>-2.4050872997839721E-2</v>
+        <v>-2.405122130220785E-2</v>
       </c>
       <c r="J15">
-        <v>8.5267156938324179E-2</v>
+        <v>8.5266453228886499E-2</v>
       </c>
       <c r="K15">
-        <v>9.0133774746307502E-2</v>
+        <v>9.0133815025032468E-2</v>
       </c>
       <c r="L15">
-        <v>0.13606005254448769</v>
+        <v>0.13606009945592221</v>
       </c>
       <c r="M15">
-        <v>0.22774902540564099</v>
+        <v>0.22774905691947431</v>
       </c>
       <c r="N15">
-        <v>0.33288180857280258</v>
+        <v>0.33288183295370788</v>
       </c>
       <c r="O15">
-        <v>0.37670493129914279</v>
+        <v>0.37670495316629732</v>
       </c>
       <c r="P15">
-        <v>0.41065195524308212</v>
+        <v>0.41065198616882481</v>
       </c>
       <c r="Q15">
-        <v>0.42595766734959561</v>
+        <v>0.42595769038004633</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1374,49 +1358,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C16">
-        <v>-3.2128254400017313E-2</v>
+        <v>-3.212825016355824E-2</v>
       </c>
       <c r="D16">
-        <v>-4.8908083025720937E-2</v>
+        <v>-4.8908075159729968E-2</v>
       </c>
       <c r="E16">
-        <v>-0.1321495142724545</v>
+        <v>-0.13214950277968621</v>
       </c>
       <c r="F16">
-        <v>-0.1337959486829032</v>
+        <v>-0.13379592680678479</v>
       </c>
       <c r="G16">
-        <v>-0.18120708749362011</v>
+        <v>-0.18120708917616801</v>
       </c>
       <c r="H16">
-        <v>-0.16770387003464651</v>
+        <v>-0.16770386191845221</v>
       </c>
       <c r="I16">
-        <v>-3.1240654157292189E-2</v>
+        <v>-3.1240643095808731E-2</v>
       </c>
       <c r="J16">
-        <v>8.9292872701355261E-2</v>
+        <v>8.929289337467905E-2</v>
       </c>
       <c r="K16">
-        <v>9.4522768796737031E-2</v>
+        <v>9.4522791752939525E-2</v>
       </c>
       <c r="L16">
-        <v>0.13456358580573041</v>
+        <v>0.1345636136661254</v>
       </c>
       <c r="M16">
-        <v>0.23600575450099401</v>
+        <v>0.23600577980826951</v>
       </c>
       <c r="N16">
-        <v>0.34486514936099449</v>
+        <v>0.3448651687301269</v>
       </c>
       <c r="O16">
-        <v>0.39440695270654458</v>
+        <v>0.39440697240745998</v>
       </c>
       <c r="P16">
-        <v>0.42527071049439708</v>
+        <v>0.4252707343574389</v>
       </c>
       <c r="Q16">
-        <v>0.4452644167506441</v>
+        <v>0.44526443313873237</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -1427,49 +1411,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C17">
-        <v>-3.6582284980212987E-2</v>
+        <v>-3.6582281658225579E-2</v>
       </c>
       <c r="D17">
-        <v>-5.4604092799943778E-2</v>
+        <v>-5.4604093498480812E-2</v>
       </c>
       <c r="E17">
-        <v>-0.14067261097012351</v>
+        <v>-0.14067260033542681</v>
       </c>
       <c r="F17">
-        <v>-0.14818844686370131</v>
+        <v>-0.14818842534719931</v>
       </c>
       <c r="G17">
-        <v>-0.18841560550341641</v>
+        <v>-0.18841560281711719</v>
       </c>
       <c r="H17">
-        <v>-0.17632276146798709</v>
+        <v>-0.17632275326910291</v>
       </c>
       <c r="I17">
-        <v>-3.9508510390010763E-2</v>
+        <v>-3.9508488807893753E-2</v>
       </c>
       <c r="J17">
-        <v>6.9147618572639763E-2</v>
+        <v>6.9147642326625458E-2</v>
       </c>
       <c r="K17">
-        <v>6.6385006526099896E-2</v>
+        <v>6.638502963959203E-2</v>
       </c>
       <c r="L17">
-        <v>0.1060623907290846</v>
+        <v>0.1060624137379409</v>
       </c>
       <c r="M17">
-        <v>0.19431045832193919</v>
+        <v>0.1943104611391327</v>
       </c>
       <c r="N17">
-        <v>0.30452947036026062</v>
+        <v>0.30452949434512039</v>
       </c>
       <c r="O17">
-        <v>0.35009075511671639</v>
+        <v>0.35009077690052931</v>
       </c>
       <c r="P17">
-        <v>0.39194918376549698</v>
+        <v>0.3919492125221723</v>
       </c>
       <c r="Q17">
-        <v>0.41770542632850249</v>
+        <v>0.41770545162945122</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1480,49 +1464,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C18">
-        <v>-2.3756067543613899E-2</v>
+        <v>-2.3756065729732351E-2</v>
       </c>
       <c r="D18">
-        <v>-7.9058614168611069E-2</v>
+        <v>-7.9058620108495695E-2</v>
       </c>
       <c r="E18">
-        <v>-8.751958323863368E-2</v>
+        <v>-8.7519584646252077E-2</v>
       </c>
       <c r="F18">
-        <v>-0.13553694558072621</v>
+        <v>-0.1355369473605138</v>
       </c>
       <c r="G18">
-        <v>7.1183916496469157E-2</v>
+        <v>7.1183927818221929E-2</v>
       </c>
       <c r="H18">
-        <v>0.19076535009557491</v>
+        <v>0.1907653608871957</v>
       </c>
       <c r="I18">
-        <v>0.25243138480867322</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0.34059576714046053</v>
+        <v>0.25243139362810141</v>
+      </c>
+      <c r="J18">
+        <v>0.34059578815624958</v>
       </c>
       <c r="K18">
-        <v>0.40652708777689323</v>
+        <v>0.40652710599893699</v>
       </c>
       <c r="L18">
-        <v>0.42502916598843782</v>
+        <v>0.42502912403192322</v>
       </c>
       <c r="M18">
-        <v>0.46147604249632479</v>
+        <v>0.46147609610972262</v>
       </c>
       <c r="N18">
-        <v>0.46247980665436988</v>
+        <v>0.46247986698914001</v>
       </c>
       <c r="O18">
-        <v>0.43908841232743651</v>
+        <v>0.439088487089902</v>
       </c>
       <c r="P18">
-        <v>0.4075689214923624</v>
+        <v>0.40756901073479368</v>
       </c>
       <c r="Q18">
-        <v>0.39362028961660672</v>
+        <v>0.39362041088060662</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1533,49 +1517,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C19">
-        <v>-2.4090244565841381E-2</v>
+        <v>-2.4090242689278049E-2</v>
       </c>
       <c r="D19">
-        <v>-7.789115949750848E-2</v>
+        <v>-7.7891167693561567E-2</v>
       </c>
       <c r="E19">
-        <v>-9.4758592183586718E-2</v>
+        <v>-9.4758570100078807E-2</v>
       </c>
       <c r="F19">
-        <v>-0.1012625582487755</v>
+        <v>-0.10126256369850239</v>
       </c>
       <c r="G19">
-        <v>0.13165676007514179</v>
+        <v>0.13165676880297669</v>
       </c>
       <c r="H19">
-        <v>0.26538264307438802</v>
+        <v>0.26538265636617359</v>
       </c>
       <c r="I19">
-        <v>0.31070789785609337</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0.39158802694322642</v>
+        <v>0.31070791300777928</v>
+      </c>
+      <c r="J19">
+        <v>0.39158804344010639</v>
       </c>
       <c r="K19">
-        <v>0.43945448334210219</v>
+        <v>0.43945450907157863</v>
       </c>
       <c r="L19">
-        <v>0.45572669705598551</v>
+        <v>0.4557265827695377</v>
       </c>
       <c r="M19">
-        <v>0.47783706620163352</v>
+        <v>0.47783709175872979</v>
       </c>
       <c r="N19">
-        <v>0.48026471719822911</v>
+        <v>0.48026474703305128</v>
       </c>
       <c r="O19">
-        <v>0.47329560430145767</v>
+        <v>0.47329563747158843</v>
       </c>
       <c r="P19">
-        <v>0.48050467460297408</v>
+        <v>0.4805047202101968</v>
       </c>
       <c r="Q19">
-        <v>0.47438743650092141</v>
+        <v>0.47438750339779001</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1586,49 +1570,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C20">
-        <v>-2.5210624954087012E-2</v>
+        <v>-2.521062285346648E-2</v>
       </c>
       <c r="D20">
-        <v>-6.7202189948162031E-2</v>
+        <v>-6.7202199818920033E-2</v>
       </c>
       <c r="E20">
-        <v>-8.5168737124641972E-2</v>
+        <v>-8.5168734044690123E-2</v>
       </c>
       <c r="F20">
-        <v>1.0385040688713411E-2</v>
+        <v>1.038504268887494E-2</v>
       </c>
       <c r="G20">
-        <v>0.16671312223890239</v>
+        <v>0.1667131300601995</v>
       </c>
       <c r="H20">
-        <v>0.2014136265641584</v>
+        <v>0.2014136422060788</v>
       </c>
       <c r="I20">
-        <v>0.30899183481191</v>
+        <v>0.30899185513048327</v>
       </c>
       <c r="J20">
-        <v>0.38139676541062623</v>
-      </c>
-      <c r="K20" s="2">
-        <v>0.41370969945143138</v>
+        <v>0.38139678163848501</v>
+      </c>
+      <c r="K20">
+        <v>0.41370982330948303</v>
       </c>
       <c r="L20">
-        <v>0.46870492804754349</v>
+        <v>0.46870496609958229</v>
       </c>
       <c r="M20">
-        <v>0.48583833243855751</v>
+        <v>0.48583835236430589</v>
       </c>
       <c r="N20">
-        <v>0.4694202807533206</v>
+        <v>0.46942029848702199</v>
       </c>
       <c r="O20">
-        <v>0.51941391332903275</v>
+        <v>0.5194139430593876</v>
       </c>
       <c r="P20">
-        <v>0.51149553953150706</v>
+        <v>0.5114955859836674</v>
       </c>
       <c r="Q20">
-        <v>0.5066515670492453</v>
+        <v>0.50665160425129874</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -1639,49 +1623,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C21">
-        <v>-2.1174623460256042E-2</v>
+        <v>-2.1174622580284349E-2</v>
       </c>
       <c r="D21">
-        <v>-3.8506677642957107E-2</v>
+        <v>-3.8506674555550152E-2</v>
       </c>
       <c r="E21">
-        <v>-0.1370404822597894</v>
+        <v>-0.13704049894549189</v>
       </c>
       <c r="F21">
-        <v>2.9142550496288239E-2</v>
+        <v>2.9142543519039429E-2</v>
       </c>
       <c r="G21">
-        <v>0.11207045341260451</v>
+        <v>0.112070442437223</v>
       </c>
       <c r="H21">
-        <v>0.1415339034862747</v>
+        <v>0.1415338686180094</v>
       </c>
       <c r="I21">
-        <v>0.1769481958881558</v>
+        <v>0.17694819713363871</v>
       </c>
       <c r="J21">
-        <v>0.22567303564964711</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0.29810304139179461</v>
+        <v>0.22567306026999859</v>
+      </c>
+      <c r="K21">
+        <v>0.29810306944639081</v>
       </c>
       <c r="L21">
-        <v>0.33544682788979829</v>
+        <v>0.33544688876497297</v>
       </c>
       <c r="M21">
-        <v>0.358431520517835</v>
+        <v>0.35843162183169991</v>
       </c>
       <c r="N21">
-        <v>0.34640200339408489</v>
+        <v>0.34640215048495532</v>
       </c>
       <c r="O21">
-        <v>0.31867495096664972</v>
+        <v>0.31867513874989101</v>
       </c>
       <c r="P21">
-        <v>0.31136396955093099</v>
+        <v>0.31136425663507711</v>
       </c>
       <c r="Q21">
-        <v>0.31683170444123188</v>
+        <v>0.31683206434129779</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1692,49 +1676,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C22">
-        <v>-2.1853971970998819E-2</v>
+        <v>-2.1853971330517589E-2</v>
       </c>
       <c r="D22">
-        <v>-4.1524660839614168E-2</v>
+        <v>-4.1524656305807588E-2</v>
       </c>
       <c r="E22">
-        <v>-0.14042674129951571</v>
+        <v>-0.1404267532979486</v>
       </c>
       <c r="F22">
-        <v>3.2250244775841208E-2</v>
+        <v>3.2250234049591639E-2</v>
       </c>
       <c r="G22">
-        <v>0.1002674167234207</v>
+        <v>0.1002674014771492</v>
       </c>
       <c r="H22">
-        <v>0.12675269611685791</v>
+        <v>0.12675270654116469</v>
       </c>
       <c r="I22">
-        <v>0.15585649536508961</v>
+        <v>0.1558565235520819</v>
       </c>
       <c r="J22">
-        <v>0.1810250657068796</v>
-      </c>
-      <c r="K22" s="2">
-        <v>0.26067326575409622</v>
+        <v>0.18102511856949299</v>
+      </c>
+      <c r="K22">
+        <v>0.26067333938362069</v>
       </c>
       <c r="L22">
-        <v>0.29959170344723662</v>
+        <v>0.29959178910908563</v>
       </c>
       <c r="M22">
-        <v>0.31973247533750698</v>
+        <v>0.31973261027946459</v>
       </c>
       <c r="N22">
-        <v>0.31818215186229809</v>
+        <v>0.31818236468385169</v>
       </c>
       <c r="O22">
-        <v>0.30851287217781859</v>
+        <v>0.30851320262251958</v>
       </c>
       <c r="P22">
-        <v>0.30929233473357381</v>
+        <v>0.3092927589052239</v>
       </c>
       <c r="Q22">
-        <v>0.30359242665530661</v>
+        <v>0.30359293903141071</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -1745,49 +1729,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C23">
-        <v>-2.075998764515289E-2</v>
+        <v>-2.0759986857734409E-2</v>
       </c>
       <c r="D23">
-        <v>-9.0065791659010769E-2</v>
+        <v>-9.0065848923880837E-2</v>
       </c>
       <c r="E23">
-        <v>5.7964283717133122E-2</v>
+        <v>5.796423039403005E-2</v>
       </c>
       <c r="F23">
-        <v>0.10708105243739741</v>
+        <v>0.10708101158103581</v>
       </c>
       <c r="G23">
-        <v>0.28236190816712081</v>
+        <v>0.28236188632339199</v>
       </c>
       <c r="H23">
-        <v>0.36993885188782522</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0.40812804974572597</v>
+        <v>0.36993884874603961</v>
+      </c>
+      <c r="I23">
+        <v>0.40812806061198847</v>
       </c>
       <c r="J23">
-        <v>0.44002175237835323</v>
+        <v>0.44002179706192729</v>
       </c>
       <c r="K23">
-        <v>0.46565103053022178</v>
+        <v>0.46565110946645127</v>
       </c>
       <c r="L23">
-        <v>0.47604944811635519</v>
+        <v>0.47604961645089389</v>
       </c>
       <c r="M23">
-        <v>0.4766983703181959</v>
+        <v>0.47669862263851048</v>
       </c>
       <c r="N23">
-        <v>0.45495381775046112</v>
+        <v>0.45495421081313969</v>
       </c>
       <c r="O23">
-        <v>0.43651517225991382</v>
+        <v>0.43651563770860979</v>
       </c>
       <c r="P23">
-        <v>0.41884805339375769</v>
+        <v>0.41884854930881299</v>
       </c>
       <c r="Q23">
-        <v>0.39361937346418963</v>
+        <v>0.39361994275437701</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -1798,49 +1782,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C24">
-        <v>-3.9445118665311578E-2</v>
+        <v>-3.9445117653746968E-2</v>
       </c>
       <c r="D24">
-        <v>-0.13750307392636649</v>
+        <v>-0.13750307622271951</v>
       </c>
       <c r="E24">
-        <v>-0.15429810777929881</v>
+        <v>-0.1542981002565757</v>
       </c>
       <c r="F24">
-        <v>-0.12580297072886051</v>
+        <v>-0.1258029674204946</v>
       </c>
       <c r="G24">
-        <v>-0.13219155533749821</v>
+        <v>-0.13219154458994839</v>
       </c>
       <c r="H24">
-        <v>-5.9800571242552537E-2</v>
+        <v>-5.9800571894684899E-2</v>
       </c>
       <c r="I24">
-        <v>-0.12566425862777861</v>
+        <v>-0.12566425519846411</v>
       </c>
       <c r="J24">
-        <v>-3.5122388929873079E-2</v>
+        <v>-3.5122356939814352E-2</v>
       </c>
       <c r="K24">
-        <v>0.15942691998486419</v>
+        <v>0.15942698392741531</v>
       </c>
       <c r="L24">
-        <v>0.22593317665289819</v>
+        <v>0.22593324672109569</v>
       </c>
       <c r="M24">
-        <v>0.26265842062076178</v>
+        <v>0.26265851974479298</v>
       </c>
       <c r="N24">
-        <v>0.24062645307844921</v>
+        <v>0.2406265954169047</v>
       </c>
       <c r="O24">
-        <v>0.17440852219163039</v>
+        <v>0.1744087433223932</v>
       </c>
       <c r="P24">
-        <v>0.1236621607726464</v>
+        <v>0.1236623933407259</v>
       </c>
       <c r="Q24">
-        <v>5.7889422342563217E-2</v>
+        <v>5.7889673623331188E-2</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -1851,49 +1835,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C25">
-        <v>-3.9777296594468603E-2</v>
+        <v>-3.9777293418867182E-2</v>
       </c>
       <c r="D25">
-        <v>-0.14668964214482461</v>
+        <v>-0.14668965337197251</v>
       </c>
       <c r="E25">
-        <v>-0.1533578638397971</v>
+        <v>-0.1533578625891889</v>
       </c>
       <c r="F25">
-        <v>-0.1146524771681655</v>
+        <v>-0.11465247225525919</v>
       </c>
       <c r="G25">
-        <v>-0.11040132119996469</v>
+        <v>-0.1104013421500827</v>
       </c>
       <c r="H25">
-        <v>-9.4466973290522532E-2</v>
+        <v>-9.4466970452539684E-2</v>
       </c>
       <c r="I25">
-        <v>-0.16652272291310249</v>
+        <v>-0.16652271598573321</v>
       </c>
       <c r="J25">
-        <v>-0.1235094222071005</v>
+        <v>-0.123509398416531</v>
       </c>
       <c r="K25">
-        <v>-3.708598462337484E-2</v>
+        <v>-3.7085953145773648E-2</v>
       </c>
       <c r="L25">
-        <v>0.1791094753449648</v>
+        <v>0.1791095328053324</v>
       </c>
       <c r="M25">
-        <v>0.21260536822661169</v>
+        <v>0.21260543567343521</v>
       </c>
       <c r="N25">
-        <v>0.24242481607851149</v>
+        <v>0.24242493598919079</v>
       </c>
       <c r="O25">
-        <v>0.20534391953058251</v>
+        <v>0.20534405023493801</v>
       </c>
       <c r="P25">
-        <v>0.1557113190798044</v>
+        <v>0.15571167041122411</v>
       </c>
       <c r="Q25">
-        <v>9.232544023041396E-2</v>
+        <v>9.2325707394342413E-2</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -1904,49 +1888,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C26">
-        <v>-3.5097712286716702E-2</v>
+        <v>-3.5097710407953453E-2</v>
       </c>
       <c r="D26">
-        <v>-0.14879105688454899</v>
+        <v>-0.14879105855500549</v>
       </c>
       <c r="E26">
-        <v>-0.12803031401314871</v>
+        <v>-0.12803031259691211</v>
       </c>
       <c r="F26">
-        <v>-7.9896874659333081E-2</v>
+        <v>-7.9896874242994298E-2</v>
       </c>
       <c r="G26">
-        <v>-0.12227197322723481</v>
+        <v>-0.1222720215886136</v>
       </c>
       <c r="H26">
-        <v>-9.0310684316499315E-2</v>
+        <v>-9.0310678106499523E-2</v>
       </c>
       <c r="I26">
-        <v>3.6102404273648747E-2</v>
+        <v>3.6102420411032059E-2</v>
       </c>
       <c r="J26">
-        <v>-2.162712005884888E-2</v>
+        <v>-2.1627102204836639E-2</v>
       </c>
       <c r="K26">
-        <v>0.12541476290537859</v>
+        <v>0.12541480281147671</v>
       </c>
       <c r="L26">
-        <v>0.22055014877228521</v>
+        <v>0.22055020845188661</v>
       </c>
       <c r="M26">
-        <v>0.22621452131920969</v>
+        <v>0.22621460992759199</v>
       </c>
       <c r="N26">
-        <v>0.1993860266546244</v>
+        <v>0.1993861876788191</v>
       </c>
       <c r="O26">
-        <v>0.1598328053354878</v>
+        <v>0.15983300686615901</v>
       </c>
       <c r="P26">
-        <v>0.1091875732390951</v>
+        <v>0.10918781841140179</v>
       </c>
       <c r="Q26">
-        <v>2.9955480566373541E-2</v>
+        <v>2.995575295616499E-2</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -1957,49 +1941,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C27">
-        <v>-4.2397773388044818E-2</v>
+        <v>-4.2397769087745271E-2</v>
       </c>
       <c r="D27">
-        <v>-0.15383300861581761</v>
+        <v>-0.153833006585951</v>
       </c>
       <c r="E27">
-        <v>-0.13115286184412711</v>
+        <v>-0.13115285868488791</v>
       </c>
       <c r="F27">
-        <v>-8.9353757599278938E-2</v>
+        <v>-8.9353747261256111E-2</v>
       </c>
       <c r="G27">
-        <v>-0.1231433059374802</v>
+        <v>-0.1231433055534126</v>
       </c>
       <c r="H27">
-        <v>-9.415957885176808E-2</v>
+        <v>-9.4159570290525949E-2</v>
       </c>
       <c r="I27">
-        <v>1.6865610991641911E-2</v>
+        <v>1.6865614307032949E-2</v>
       </c>
       <c r="J27">
-        <v>-2.553581902148705E-2</v>
+        <v>-2.5535796693541741E-2</v>
       </c>
       <c r="K27">
-        <v>0.1067170811013983</v>
+        <v>0.10671710472772521</v>
       </c>
       <c r="L27">
-        <v>0.26213123495200819</v>
+        <v>0.26213129706204358</v>
       </c>
       <c r="M27">
-        <v>0.29765731605259721</v>
+        <v>0.29765738941777869</v>
       </c>
       <c r="N27">
-        <v>0.30436050077153037</v>
+        <v>0.30436060803439802</v>
       </c>
       <c r="O27">
-        <v>0.31459199577835639</v>
+        <v>0.31459211944413568</v>
       </c>
       <c r="P27">
-        <v>0.29381747684173459</v>
+        <v>0.29381765134603582</v>
       </c>
       <c r="Q27">
-        <v>0.28189050314478081</v>
+        <v>0.28189068281315582</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -2010,49 +1994,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C28">
-        <v>-3.784190472112952E-2</v>
+        <v>-3.7841901065829971E-2</v>
       </c>
       <c r="D28">
-        <v>-0.13832858407417589</v>
+        <v>-0.1383285880651218</v>
       </c>
       <c r="E28">
-        <v>-0.1484779268095717</v>
+        <v>-0.14847792022206541</v>
       </c>
       <c r="F28">
-        <v>-0.1105304560027613</v>
+        <v>-0.1105304495465612</v>
       </c>
       <c r="G28">
-        <v>-0.10473490231742801</v>
+        <v>-0.10473491145973381</v>
       </c>
       <c r="H28">
-        <v>-8.4908990926140557E-2</v>
+        <v>-8.4908993081280179E-2</v>
       </c>
       <c r="I28">
-        <v>-0.13677070765079161</v>
+        <v>-0.1367707060718564</v>
       </c>
       <c r="J28">
-        <v>-0.1117303173615906</v>
+        <v>-0.1117303029179762</v>
       </c>
       <c r="K28">
-        <v>-3.349959485105114E-2</v>
+        <v>-3.349956968306729E-2</v>
       </c>
       <c r="L28">
-        <v>0.19547600202477011</v>
+        <v>0.1954760622715763</v>
       </c>
       <c r="M28">
-        <v>0.25339280145519438</v>
+        <v>0.25339287610184941</v>
       </c>
       <c r="N28">
-        <v>0.26572643567535642</v>
+        <v>0.26572652737854929</v>
       </c>
       <c r="O28">
-        <v>0.27036663591825438</v>
+        <v>0.27036674323538751</v>
       </c>
       <c r="P28">
-        <v>0.24920426205017859</v>
+        <v>0.24920439471795311</v>
       </c>
       <c r="Q28">
-        <v>0.25130323487400208</v>
+        <v>0.25130339872573659</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -2063,49 +2047,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C29">
-        <v>-4.0553326876614677E-2</v>
+        <v>-4.0553323869142788E-2</v>
       </c>
       <c r="D29">
-        <v>-0.1479538162195814</v>
+        <v>-0.14795381723129719</v>
       </c>
       <c r="E29">
-        <v>-0.15743990045793591</v>
+        <v>-0.15743989414484519</v>
       </c>
       <c r="F29">
-        <v>-0.12338240862939261</v>
+        <v>-0.1233824043914946</v>
       </c>
       <c r="G29">
-        <v>-0.11226507714031531</v>
+        <v>-0.1122650929425321</v>
       </c>
       <c r="H29">
-        <v>-9.217840080306676E-2</v>
+        <v>-9.2178402100686757E-2</v>
       </c>
       <c r="I29">
-        <v>-0.14017573173242789</v>
+        <v>-0.1401757267375508</v>
       </c>
       <c r="J29">
-        <v>-0.1197166476653018</v>
+        <v>-0.1197166368532586</v>
       </c>
       <c r="K29">
-        <v>-4.7758584417506571E-2</v>
+        <v>-4.7758563081416808E-2</v>
       </c>
       <c r="L29">
-        <v>0.21084603881324121</v>
+        <v>0.21084609406124169</v>
       </c>
       <c r="M29">
-        <v>0.26673410807023251</v>
+        <v>0.26673417590672621</v>
       </c>
       <c r="N29">
-        <v>0.29311776172071929</v>
+        <v>0.2931178468116154</v>
       </c>
       <c r="O29">
-        <v>0.30076538012438409</v>
+        <v>0.30076548560564648</v>
       </c>
       <c r="P29">
-        <v>0.2916632986213416</v>
+        <v>0.29166347821874211</v>
       </c>
       <c r="Q29">
-        <v>0.2996887411334816</v>
+        <v>0.29968889769792301</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -2116,49 +2100,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C30">
-        <v>-3.831418182318809E-2</v>
+        <v>-3.831417789801763E-2</v>
       </c>
       <c r="D30">
-        <v>-0.14302718790381119</v>
+        <v>-0.14302719526659141</v>
       </c>
       <c r="E30">
-        <v>-0.15614759837233461</v>
+        <v>-0.15614759556024069</v>
       </c>
       <c r="F30">
-        <v>-0.12049862851248461</v>
+        <v>-0.1204986238320105</v>
       </c>
       <c r="G30">
-        <v>-0.11542928046734501</v>
+        <v>-0.115429291985469</v>
       </c>
       <c r="H30">
-        <v>-9.097631206091919E-2</v>
+        <v>-9.0976311190799408E-2</v>
       </c>
       <c r="I30">
-        <v>-0.15390521041131441</v>
+        <v>-0.1539052115419052</v>
       </c>
       <c r="J30">
-        <v>-0.1350466831810582</v>
+        <v>-0.13504668996925831</v>
       </c>
       <c r="K30">
-        <v>-6.1618431112419048E-2</v>
+        <v>-6.1618424221266052E-2</v>
       </c>
       <c r="L30">
-        <v>0.20021368233568659</v>
+        <v>0.20021373055609271</v>
       </c>
       <c r="M30">
-        <v>0.25418407903060369</v>
+        <v>0.25418413856555933</v>
       </c>
       <c r="N30">
-        <v>0.27866226840155078</v>
+        <v>0.2786623438566127</v>
       </c>
       <c r="O30">
-        <v>0.28782913077550948</v>
+        <v>0.2878292114540254</v>
       </c>
       <c r="P30">
-        <v>0.28789339018815191</v>
+        <v>0.28789348391854802</v>
       </c>
       <c r="Q30">
-        <v>0.30260014931532342</v>
+        <v>0.30260026933995637</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -2169,49 +2153,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C31">
-        <v>-4.2422741215078393E-2</v>
+        <v>-4.2422739102868798E-2</v>
       </c>
       <c r="D31">
-        <v>-0.14491231685552011</v>
+        <v>-0.14491231699162521</v>
       </c>
       <c r="E31">
-        <v>-0.1537228337438859</v>
+        <v>-0.15372282746792071</v>
       </c>
       <c r="F31">
-        <v>-0.11785106946828761</v>
+        <v>-0.1178510613871207</v>
       </c>
       <c r="G31">
-        <v>-0.1102408660278711</v>
+        <v>-0.1102408772198878</v>
       </c>
       <c r="H31">
-        <v>-8.5539583889990667E-2</v>
+        <v>-8.553958021073535E-2</v>
       </c>
       <c r="I31">
-        <v>-0.13736251335144309</v>
+        <v>-0.13736250908203851</v>
       </c>
       <c r="J31">
-        <v>-0.1193058994781326</v>
+        <v>-0.1193058809055404</v>
       </c>
       <c r="K31">
-        <v>-4.7607132409206533E-2</v>
+        <v>-4.7607113703182789E-2</v>
       </c>
       <c r="L31">
-        <v>0.19420506203296989</v>
+        <v>0.19420511125112391</v>
       </c>
       <c r="M31">
-        <v>0.25542254903204847</v>
+        <v>0.25542260827834701</v>
       </c>
       <c r="N31">
-        <v>0.28022837561489577</v>
+        <v>0.28022843809663361</v>
       </c>
       <c r="O31">
-        <v>0.29944601812110871</v>
+        <v>0.29944608684325258</v>
       </c>
       <c r="P31">
-        <v>0.29294318178999251</v>
+        <v>0.29294320096314153</v>
       </c>
       <c r="Q31">
-        <v>0.31262369790353478</v>
+        <v>0.31262378337214419</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -2222,49 +2206,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C32">
-        <v>-3.9930359939206357E-2</v>
+        <v>-3.9930356365712238E-2</v>
       </c>
       <c r="D32">
-        <v>-0.1465127467827731</v>
+        <v>-0.14651274541339099</v>
       </c>
       <c r="E32">
-        <v>-0.15867130046508671</v>
+        <v>-0.15867129371685629</v>
       </c>
       <c r="F32">
-        <v>-0.1238106440316538</v>
+        <v>-0.123810638727119</v>
       </c>
       <c r="G32">
-        <v>-0.1138376360943303</v>
+        <v>-0.1138376392837093</v>
       </c>
       <c r="H32">
-        <v>-8.9044001999902242E-2</v>
+        <v>-8.9043999877861185E-2</v>
       </c>
       <c r="I32">
-        <v>-0.15370217589589791</v>
+        <v>-0.15370217142916551</v>
       </c>
       <c r="J32">
-        <v>-0.1046709616488484</v>
+        <v>-0.1046709459425882</v>
       </c>
       <c r="K32">
-        <v>-3.2059657977283093E-2</v>
+        <v>-3.2059631136027417E-2</v>
       </c>
       <c r="L32">
-        <v>0.1947871721389815</v>
+        <v>0.19478724131629449</v>
       </c>
       <c r="M32">
-        <v>0.25285255574778492</v>
+        <v>0.25285264757430409</v>
       </c>
       <c r="N32">
-        <v>0.2748833047793221</v>
+        <v>0.27488342082252831</v>
       </c>
       <c r="O32">
-        <v>0.26755114029377491</v>
+        <v>0.26755127201627182</v>
       </c>
       <c r="P32">
-        <v>0.23502528348344109</v>
+        <v>0.23502545447041071</v>
       </c>
       <c r="Q32">
-        <v>0.2216042435995759</v>
+        <v>0.22160447411245959</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -2275,49 +2259,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C33">
-        <v>-4.1226438291630238E-2</v>
+        <v>-4.1226434318130042E-2</v>
       </c>
       <c r="D33">
-        <v>-0.1516714023690903</v>
+        <v>-0.15167141156264149</v>
       </c>
       <c r="E33">
-        <v>-0.1649546506758251</v>
+        <v>-0.16495464546846389</v>
       </c>
       <c r="F33">
-        <v>-0.12788141077995269</v>
+        <v>-0.12788140203365581</v>
       </c>
       <c r="G33">
-        <v>-0.1153150275457443</v>
+        <v>-0.11531504402864851</v>
       </c>
       <c r="H33">
-        <v>-9.4274230545046689E-2</v>
+        <v>-9.4274235271546866E-2</v>
       </c>
       <c r="I33">
-        <v>-0.1539660306036181</v>
+        <v>-0.15396602855228861</v>
       </c>
       <c r="J33">
-        <v>-0.11487675357554381</v>
+        <v>-0.11487674782874339</v>
       </c>
       <c r="K33">
-        <v>-4.3309287835111752E-2</v>
+        <v>-4.3309264792086022E-2</v>
       </c>
       <c r="L33">
-        <v>0.20690325765777251</v>
+        <v>0.20690331908809079</v>
       </c>
       <c r="M33">
-        <v>0.25706716129850488</v>
+        <v>0.25706724409141002</v>
       </c>
       <c r="N33">
-        <v>0.27905128009925079</v>
+        <v>0.27905137810137598</v>
       </c>
       <c r="O33">
-        <v>0.26964248250227141</v>
+        <v>0.26964260500246262</v>
       </c>
       <c r="P33">
-        <v>0.2451782876971271</v>
+        <v>0.24517844405572239</v>
       </c>
       <c r="Q33">
-        <v>0.22753724503712161</v>
+        <v>0.22753743186638609</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -2328,49 +2312,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C34">
-        <v>-4.1074718625314442E-2</v>
+        <v>-4.1074713911075617E-2</v>
       </c>
       <c r="D34">
-        <v>-0.14724295200378071</v>
+        <v>-0.14724295183046099</v>
       </c>
       <c r="E34">
-        <v>-0.1603009167988951</v>
+        <v>-0.1603009094227566</v>
       </c>
       <c r="F34">
-        <v>-0.1257114164204283</v>
+        <v>-0.1257114099298571</v>
       </c>
       <c r="G34">
-        <v>-0.11544802432454949</v>
+        <v>-0.1154480005302935</v>
       </c>
       <c r="H34">
-        <v>-8.9146536317300476E-2</v>
+        <v>-8.9146538787700375E-2</v>
       </c>
       <c r="I34">
-        <v>-0.14307748280130311</v>
+        <v>-0.14307748570512641</v>
       </c>
       <c r="J34">
-        <v>-0.1139687374578484</v>
+        <v>-0.1139687075811484</v>
       </c>
       <c r="K34">
-        <v>-5.1603352150574613E-2</v>
+        <v>-5.1603327332943517E-2</v>
       </c>
       <c r="L34">
-        <v>0.1885443579908293</v>
+        <v>0.18854442430111881</v>
       </c>
       <c r="M34">
-        <v>0.2472954703415618</v>
+        <v>0.2472955526713726</v>
       </c>
       <c r="N34">
-        <v>0.27760736982739709</v>
+        <v>0.2776074679277018</v>
       </c>
       <c r="O34">
-        <v>0.27589761357676612</v>
+        <v>0.27589772828579578</v>
       </c>
       <c r="P34">
-        <v>0.25572119833032941</v>
+        <v>0.25572134513055739</v>
       </c>
       <c r="Q34">
-        <v>0.25001437574410817</v>
+        <v>0.25001455058431199</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -2381,49 +2365,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C35">
-        <v>-3.8950254876399068E-2</v>
+        <v>-3.8950251505011899E-2</v>
       </c>
       <c r="D35">
-        <v>-0.14619186951923069</v>
+        <v>-0.14619187018002769</v>
       </c>
       <c r="E35">
-        <v>-0.15832109244478121</v>
+        <v>-0.15832108548847601</v>
       </c>
       <c r="F35">
-        <v>-0.12388812181905889</v>
+        <v>-0.12388811557186991</v>
       </c>
       <c r="G35">
-        <v>-0.118058327673457</v>
+        <v>-0.1180583431945996</v>
       </c>
       <c r="H35">
-        <v>-9.3662158009411287E-2</v>
+        <v>-9.3662182178177705E-2</v>
       </c>
       <c r="I35">
-        <v>-0.1425697226495812</v>
+        <v>-0.1425697081024796</v>
       </c>
       <c r="J35">
-        <v>-0.1107170773503912</v>
+        <v>-0.1107170672085586</v>
       </c>
       <c r="K35">
-        <v>-4.4079106632974499E-2</v>
+        <v>-4.4079088732337082E-2</v>
       </c>
       <c r="L35">
-        <v>0.206552472395126</v>
+        <v>0.20655252346401401</v>
       </c>
       <c r="M35">
-        <v>0.26260873769053</v>
+        <v>0.26260880373968332</v>
       </c>
       <c r="N35">
-        <v>0.28981143243686253</v>
+        <v>0.28981151710473169</v>
       </c>
       <c r="O35">
-        <v>0.28956317209979188</v>
+        <v>0.28956326018623307</v>
       </c>
       <c r="P35">
-        <v>0.27463999330015482</v>
+        <v>0.27464010813377271</v>
       </c>
       <c r="Q35">
-        <v>0.26760676563451169</v>
+        <v>0.26760691747887588</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -2434,49 +2418,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C36">
-        <v>-4.0888338554719593E-2</v>
+        <v>-4.0888331078335158E-2</v>
       </c>
       <c r="D36">
-        <v>-0.15019906974330749</v>
+        <v>-0.1501990668105069</v>
       </c>
       <c r="E36">
-        <v>-0.16442235868016819</v>
+        <v>-0.16442235308362901</v>
       </c>
       <c r="F36">
-        <v>-0.12709331955034059</v>
+        <v>-0.12709331958200151</v>
       </c>
       <c r="G36">
-        <v>-0.1160448961145298</v>
+        <v>-0.1160449037262717</v>
       </c>
       <c r="H36">
-        <v>-8.9163496589467775E-2</v>
+        <v>-8.9163484606672158E-2</v>
       </c>
       <c r="I36">
-        <v>-0.14198023397930781</v>
+        <v>-0.14198027217189019</v>
       </c>
       <c r="J36">
-        <v>-0.1160937129387354</v>
+        <v>-0.11609369814962781</v>
       </c>
       <c r="K36">
-        <v>-5.2889113977765821E-2</v>
+        <v>-5.2889100125996708E-2</v>
       </c>
       <c r="L36">
-        <v>0.18620915505921221</v>
+        <v>0.18620920681491701</v>
       </c>
       <c r="M36">
-        <v>0.24103757684532201</v>
+        <v>0.24103763298944239</v>
       </c>
       <c r="N36">
-        <v>0.27686260342530028</v>
+        <v>0.27686266655348057</v>
       </c>
       <c r="O36">
-        <v>0.29397230279253911</v>
+        <v>0.29397238264340769</v>
       </c>
       <c r="P36">
-        <v>0.29091898041305581</v>
+        <v>0.29091906662425349</v>
       </c>
       <c r="Q36">
-        <v>0.30799879370042921</v>
+        <v>0.30799889493794391</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -2487,49 +2471,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C37">
-        <v>-4.4113674927854563E-2</v>
+        <v>-4.4113668352507837E-2</v>
       </c>
       <c r="D37">
-        <v>-0.175483125865217</v>
+        <v>-0.17548313661302939</v>
       </c>
       <c r="E37">
-        <v>-0.11802818912202449</v>
+        <v>-0.1180281404629052</v>
       </c>
       <c r="F37">
-        <v>-6.9351008383463933E-2</v>
+        <v>-6.9350964261526496E-2</v>
       </c>
       <c r="G37">
-        <v>-8.2934323840841956E-2</v>
+        <v>-8.2934250818829242E-2</v>
       </c>
       <c r="H37">
-        <v>-7.1953488757154085E-2</v>
+        <v>-7.1953337915740545E-2</v>
       </c>
       <c r="I37">
-        <v>2.3893056001588989E-2</v>
+        <v>2.3893324192988959E-2</v>
       </c>
       <c r="J37">
-        <v>3.7510526644607987E-2</v>
+        <v>3.7510802072269978E-2</v>
       </c>
       <c r="K37">
-        <v>4.1388868770309471E-2</v>
+        <v>4.1389131695451539E-2</v>
       </c>
       <c r="L37">
-        <v>6.5777093693206404E-2</v>
+        <v>6.5777277944746138E-2</v>
       </c>
       <c r="M37">
-        <v>5.4300084127794537E-2</v>
+        <v>5.4300371568012158E-2</v>
       </c>
       <c r="N37">
-        <v>1.676680796652711E-2</v>
+        <v>1.6770388045024811E-2</v>
       </c>
       <c r="O37">
-        <v>5.5579052844758309E-2</v>
+        <v>5.5579319322966822E-2</v>
       </c>
       <c r="P37">
-        <v>7.964499935825782E-2</v>
+        <v>7.964542489521538E-2</v>
       </c>
       <c r="Q37">
-        <v>9.3786713005232128E-2</v>
+        <v>9.3787308386547863E-2</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -2540,49 +2524,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C38">
-        <v>-4.1883431641257289E-2</v>
+        <v>-4.1883425517003303E-2</v>
       </c>
       <c r="D38">
-        <v>-0.15445228235198319</v>
+        <v>-0.15445228749166631</v>
       </c>
       <c r="E38">
-        <v>-0.12784625387170359</v>
+        <v>-0.12784624140588161</v>
       </c>
       <c r="F38">
-        <v>-4.0565253910211402E-2</v>
+        <v>-4.0565262983788333E-2</v>
       </c>
       <c r="G38">
-        <v>2.8011579037234939E-2</v>
+        <v>2.8011599196157162E-2</v>
       </c>
       <c r="H38">
-        <v>0.1221403107065583</v>
+        <v>0.1221403587938286</v>
       </c>
       <c r="I38">
-        <v>0.26156140484610091</v>
+        <v>0.26156148260983081</v>
       </c>
       <c r="J38">
-        <v>0.24719653218532939</v>
+        <v>0.24719666633837201</v>
       </c>
       <c r="K38">
-        <v>0.20448935939244009</v>
+        <v>0.20448953139750331</v>
       </c>
       <c r="L38">
-        <v>0.1839617255291692</v>
+        <v>0.18396192299791789</v>
       </c>
       <c r="M38">
-        <v>0.1972729978514326</v>
+        <v>0.19727321761874961</v>
       </c>
       <c r="N38">
-        <v>0.20154332563146729</v>
+        <v>0.20154352518796581</v>
       </c>
       <c r="O38">
-        <v>0.23716393375164671</v>
+        <v>0.2371640590564052</v>
       </c>
       <c r="P38">
-        <v>0.26205071389851903</v>
+        <v>0.26205088198078391</v>
       </c>
       <c r="Q38">
-        <v>0.2671213185713931</v>
+        <v>0.26712149378368899</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -2593,49 +2577,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C39">
-        <v>-4.3500613226694879E-2</v>
+        <v>-4.3500612753008212E-2</v>
       </c>
       <c r="D39">
-        <v>-0.15177463102381569</v>
+        <v>-0.1517746390815112</v>
       </c>
       <c r="E39">
-        <v>-0.12023340205068039</v>
+        <v>-0.1202334030118983</v>
       </c>
       <c r="F39">
-        <v>-2.59626656364405E-2</v>
+        <v>-2.5962755478086939E-2</v>
       </c>
       <c r="G39">
-        <v>1.202174813282653E-2</v>
+        <v>1.202151099338742E-2</v>
       </c>
       <c r="H39">
-        <v>9.8782147739196469E-2</v>
+        <v>9.8782160973481442E-2</v>
       </c>
       <c r="I39">
-        <v>0.22914328601230249</v>
+        <v>0.22914332537372181</v>
       </c>
       <c r="J39">
-        <v>0.23388777809278949</v>
+        <v>0.23388768391744821</v>
       </c>
       <c r="K39">
-        <v>0.2481730872492991</v>
+        <v>0.24817308421298481</v>
       </c>
       <c r="L39">
-        <v>0.2509705945330406</v>
+        <v>0.250970722729285</v>
       </c>
       <c r="M39">
-        <v>0.25454335078558638</v>
+        <v>0.25454345632551167</v>
       </c>
       <c r="N39">
-        <v>0.28759747598024321</v>
+        <v>0.28759761015984708</v>
       </c>
       <c r="O39">
-        <v>0.29235512084607462</v>
+        <v>0.29235529966105328</v>
       </c>
       <c r="P39">
-        <v>0.2845620359837035</v>
+        <v>0.28456222032646761</v>
       </c>
       <c r="Q39">
-        <v>0.29291609845912681</v>
+        <v>0.29291631779592481</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -2646,49 +2630,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C40">
-        <v>-6.2947686544932269E-2</v>
+        <v>-6.2947676768261893E-2</v>
       </c>
       <c r="D40">
-        <v>-8.0590003236113344E-2</v>
+        <v>-8.0590003529615123E-2</v>
       </c>
       <c r="E40">
-        <v>8.9044704630449247E-3</v>
+        <v>8.9044743886788277E-3</v>
       </c>
       <c r="F40">
-        <v>-2.902724034806773E-2</v>
+        <v>-2.902726708639684E-2</v>
       </c>
       <c r="G40">
-        <v>8.3371800345987013E-2</v>
+        <v>8.3371853754735284E-2</v>
       </c>
       <c r="H40">
-        <v>0.1493010931918449</v>
+        <v>0.14930117076048419</v>
       </c>
       <c r="I40">
-        <v>0.115824183607929</v>
+        <v>0.11582435386659511</v>
       </c>
       <c r="J40">
-        <v>6.6237636918007894E-2</v>
+        <v>6.6237870691255293E-2</v>
       </c>
       <c r="K40">
-        <v>8.5765026763350488E-2</v>
+        <v>8.5765170118046394E-2</v>
       </c>
       <c r="L40">
-        <v>0.13760204355872591</v>
+        <v>0.13760227484166729</v>
       </c>
       <c r="M40">
-        <v>0.14748476775318539</v>
+        <v>0.14748490073055981</v>
       </c>
       <c r="N40">
-        <v>0.17806124672047419</v>
+        <v>0.17806139615541819</v>
       </c>
       <c r="O40">
-        <v>0.1740535842982604</v>
+        <v>0.17405384701126331</v>
       </c>
       <c r="P40">
-        <v>0.1410756782304598</v>
+        <v>0.14107605045315821</v>
       </c>
       <c r="Q40">
-        <v>8.1874842195512582E-2</v>
+        <v>8.1875356750094927E-2</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -2699,49 +2683,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C41">
-        <v>-5.7688305220132158E-2</v>
+        <v>-5.7688300049711122E-2</v>
       </c>
       <c r="D41">
-        <v>-0.23164583237433509</v>
+        <v>-0.23164583082977691</v>
       </c>
       <c r="E41">
-        <v>-0.15477045682602419</v>
+        <v>-0.1547704510342178</v>
       </c>
       <c r="F41">
-        <v>-0.20298565679968489</v>
+        <v>-0.20298563941518061</v>
       </c>
       <c r="G41">
-        <v>-0.13063326587725549</v>
+        <v>-0.13063327118893919</v>
       </c>
       <c r="H41">
-        <v>-0.12575524064482521</v>
+        <v>-0.12575525711784619</v>
       </c>
       <c r="I41">
-        <v>-8.9881194713371013E-2</v>
+        <v>-8.9881203938190421E-2</v>
       </c>
       <c r="J41">
-        <v>-1.1358904552366E-2</v>
+        <v>-1.135890990250751E-2</v>
       </c>
       <c r="K41">
-        <v>-5.1685224126954372E-2</v>
+        <v>-5.1685240896283083E-2</v>
       </c>
       <c r="L41">
-        <v>-7.9862000623029908E-2</v>
+        <v>-7.9861992887017633E-2</v>
       </c>
       <c r="M41">
-        <v>-7.1178431259326297E-2</v>
+        <v>-7.117839174226516E-2</v>
       </c>
       <c r="N41">
-        <v>-0.10133037591420491</v>
+        <v>-0.1013302971467334</v>
       </c>
       <c r="O41">
-        <v>-0.15828359397581809</v>
+        <v>-0.15828352780028421</v>
       </c>
       <c r="P41">
-        <v>-0.15462502713086229</v>
+        <v>-0.15462493611843839</v>
       </c>
       <c r="Q41">
-        <v>-0.16325357741323099</v>
+        <v>-0.16325348406582599</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -2752,49 +2736,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C42">
-        <v>-1.9069287103967009E-2</v>
+        <v>-1.9069287134258261E-2</v>
       </c>
       <c r="D42">
-        <v>-0.10778165519950569</v>
+        <v>-0.10778164737876821</v>
       </c>
       <c r="E42">
-        <v>-0.21488466458987551</v>
+        <v>-0.21488470160173409</v>
       </c>
       <c r="F42">
-        <v>1.511624141421453E-2</v>
+        <v>1.5116251208281089E-2</v>
       </c>
       <c r="G42">
-        <v>0.1306858090360575</v>
+        <v>0.1306857861649858</v>
       </c>
       <c r="H42">
-        <v>0.17993259341140319</v>
+        <v>0.17993254751958279</v>
       </c>
       <c r="I42">
-        <v>0.30485572106898279</v>
+        <v>0.30485569915559652</v>
       </c>
       <c r="J42">
-        <v>0.31284989829595722</v>
+        <v>0.31284986560888522</v>
       </c>
       <c r="K42">
-        <v>0.29441603808694689</v>
+        <v>0.29441600261490591</v>
       </c>
       <c r="L42">
-        <v>0.34776030632228289</v>
+        <v>0.34776028031599132</v>
       </c>
       <c r="M42">
-        <v>0.35605216296757869</v>
+        <v>0.35605214551071118</v>
       </c>
       <c r="N42">
-        <v>0.34436683625294201</v>
+        <v>0.34436683828112291</v>
       </c>
       <c r="O42">
-        <v>0.33593094280302832</v>
+        <v>0.33593095163286663</v>
       </c>
       <c r="P42">
-        <v>0.33697768078189361</v>
+        <v>0.33697771148250227</v>
       </c>
       <c r="Q42">
-        <v>0.32344020538308171</v>
+        <v>0.32344018383280598</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -2805,49 +2789,49 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="C43">
-        <v>-2.8114284332585809E-2</v>
+        <v>-2.8114281789071729E-2</v>
       </c>
       <c r="D43">
-        <v>-0.1048979121825331</v>
+        <v>-0.1048979155820612</v>
       </c>
       <c r="E43">
-        <v>-8.3253286653680397E-2</v>
+        <v>-8.3253270603570642E-2</v>
       </c>
       <c r="F43">
-        <v>3.6544672004669002E-2</v>
+        <v>3.6544672032378538E-2</v>
       </c>
       <c r="G43">
-        <v>0.1839319398098265</v>
+        <v>0.18393191564202299</v>
       </c>
       <c r="H43">
-        <v>0.21354510291239551</v>
+        <v>0.21354508900784711</v>
       </c>
       <c r="I43">
-        <v>0.26831085959738321</v>
+        <v>0.26831084338092742</v>
       </c>
       <c r="J43">
-        <v>0.27569443569344448</v>
+        <v>0.27569443082205602</v>
       </c>
       <c r="K43">
-        <v>0.2409840730559126</v>
+        <v>0.2409840502016235</v>
       </c>
       <c r="L43">
-        <v>0.27050098016592888</v>
+        <v>0.27050099171046271</v>
       </c>
       <c r="M43">
-        <v>0.28011319188975842</v>
+        <v>0.28011321925171151</v>
       </c>
       <c r="N43">
-        <v>0.27275574364154909</v>
+        <v>0.27275579249228599</v>
       </c>
       <c r="O43">
-        <v>0.24948657488714179</v>
+        <v>0.24948664609493729</v>
       </c>
       <c r="P43">
-        <v>0.2214473741214405</v>
+        <v>0.22144746985028399</v>
       </c>
       <c r="Q43">
-        <v>0.20263714220101439</v>
+        <v>0.2026372716096049</v>
       </c>
     </row>
   </sheetData>
